--- a/2024/validation/Table_2_2024.xlsx
+++ b/2024/validation/Table_2_2024.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nmgov-my.sharepoint.com/personal/brad_wolaver_ose_nm_gov/Documents/Documents/_Projects/_APPs/RG/City_Santa_Fe/Buckman/Reporting/2024 Depletion Memo/TABLES/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\bradwolaver\projects\rg\santafe\2024\validation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="58" documentId="8_{C7FF6927-192B-4B82-8A60-42C77DCB84D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2833CF3-FBCE-48D0-84D5-E2480A5D802E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{277BD8CE-5698-49DD-A5CD-8F42B57FBDA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{0F8CB352-0E39-456B-B6A9-C06D7148B2FD}"/>
+    <workbookView xWindow="29535" yWindow="810" windowWidth="25455" windowHeight="15585" xr2:uid="{0F8CB352-0E39-456B-B6A9-C06D7148B2FD}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_2_2024" sheetId="1" r:id="rId1"/>
@@ -212,7 +212,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -395,12 +395,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -606,7 +600,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -633,10 +627,6 @@
     </xf>
     <xf numFmtId="4" fontId="0" fillId="33" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="34" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="43">
@@ -695,10 +685,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1172,50 +1158,50 @@
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="14">
+      <c r="A4" s="9">
         <v>3</v>
       </c>
-      <c r="B4" s="15">
-        <v>0</v>
-      </c>
-      <c r="C4" s="15">
+      <c r="B4" s="10">
+        <v>0</v>
+      </c>
+      <c r="C4" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="D4" s="15">
+      <c r="D4" s="10">
         <v>0.06</v>
       </c>
-      <c r="E4" s="15">
+      <c r="E4" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="F4" s="15">
+      <c r="F4" s="10">
         <v>0.38</v>
       </c>
-      <c r="G4" s="15">
+      <c r="G4" s="10">
         <v>23.11</v>
       </c>
-      <c r="H4" s="15">
+      <c r="H4" s="10">
         <v>0.79</v>
       </c>
-      <c r="I4" s="15">
+      <c r="I4" s="10">
         <v>8.5399999999999991</v>
       </c>
-      <c r="J4" s="15">
+      <c r="J4" s="10">
         <v>0.05</v>
       </c>
-      <c r="K4" s="15">
+      <c r="K4" s="10">
         <v>6.38</v>
       </c>
-      <c r="L4" s="15">
+      <c r="L4" s="10">
         <v>16.73</v>
       </c>
-      <c r="M4" s="15">
+      <c r="M4" s="10">
         <v>0.05</v>
       </c>
-      <c r="N4" s="15">
+      <c r="N4" s="10">
         <f t="shared" si="0"/>
         <v>56.22999999999999</v>
       </c>
-      <c r="O4" s="14">
+      <c r="O4" s="9">
         <v>3</v>
       </c>
     </row>
@@ -1771,7 +1757,7 @@
         <f>SUM(N11:N14)</f>
         <v>386.86</v>
       </c>
-      <c r="R15" s="16">
+      <c r="R15" s="14">
         <f>Q15/N15</f>
         <v>0.28177282493899997</v>
       </c>
@@ -1779,7 +1765,7 @@
         <f>N2+N8+N9</f>
         <v>713.75</v>
       </c>
-      <c r="T15" s="16">
+      <c r="T15" s="14">
         <f>S15/N15</f>
         <v>0.51986598200954148</v>
       </c>
